--- a/data/input/Jerarquia_sample.xlsx
+++ b/data/input/Jerarquia_sample.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
   <si>
     <t>Jerarquía</t>
   </si>
@@ -157,19 +157,34 @@
     <t>CR13212</t>
   </si>
   <si>
-    <t>47-AGRONOMIA</t>
-  </si>
-  <si>
-    <t>58-TALAR</t>
-  </si>
-  <si>
-    <t>153-TIGRE</t>
-  </si>
-  <si>
-    <t>237-MELO</t>
-  </si>
-  <si>
-    <t>CR13287-PAULINA</t>
+    <t>995-SE5</t>
+  </si>
+  <si>
+    <t>993-SE3</t>
+  </si>
+  <si>
+    <t>992-SE2</t>
+  </si>
+  <si>
+    <t>994-SE4</t>
+  </si>
+  <si>
+    <t>991-SE1</t>
+  </si>
+  <si>
+    <t>99543A</t>
+  </si>
+  <si>
+    <t>99315A</t>
+  </si>
+  <si>
+    <t>99212A</t>
+  </si>
+  <si>
+    <t>99434A</t>
+  </si>
+  <si>
+    <t>99111A</t>
   </si>
   <si>
     <t>4716A</t>
@@ -184,13 +199,13 @@
     <t>23748A</t>
   </si>
   <si>
+    <t>CR13212A</t>
+  </si>
+  <si>
+    <t>36372A</t>
+  </si>
+  <si>
     <t>13212A</t>
-  </si>
-  <si>
-    <t>CR13212A</t>
-  </si>
-  <si>
-    <t>36372A</t>
   </si>
 </sst>
 </file>
@@ -548,647 +563,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1">
-        <v>416</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:9">
+      <c r="A2">
         <v>4716</v>
       </c>
-      <c r="F2">
+      <c r="E2">
         <v>4716</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
         <v>47</v>
       </c>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
       <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>1225</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
         <v>31</v>
+      </c>
+      <c r="D3">
+        <v>5822</v>
       </c>
       <c r="E3">
         <v>5822</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4">
         <v>5822</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>1226</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
       </c>
       <c r="E4">
         <v>5822</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5">
         <v>5822</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F5" t="s">
         <v>48</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H5" t="s">
         <v>53</v>
       </c>
-      <c r="J4" t="s">
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>5822</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1">
-        <v>1227</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>5822</v>
-      </c>
-      <c r="G5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1">
-        <v>1228</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6">
-        <v>5822</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
       <c r="I6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>3246</v>
-      </c>
-      <c r="B7">
-        <v>15326</v>
-      </c>
-      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>15326</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="F7">
-        <v>15326</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="E7">
+        <v>15326</v>
+      </c>
+      <c r="F7" t="s">
         <v>49</v>
       </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
       <c r="I7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>15326</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
         <v>54</v>
       </c>
-      <c r="J7" t="s">
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9">
+        <v>15326</v>
+      </c>
+      <c r="E9">
+        <v>15326</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
-        <v>3247</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>15326</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>15326</v>
+      </c>
+      <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H10" t="s">
         <v>54</v>
       </c>
-      <c r="J8" t="s">
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>15326</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1">
-        <v>3248</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="I11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>15326</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>15326</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>15326</v>
+      </c>
+      <c r="E14">
+        <v>15326</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="E9">
-        <v>15326</v>
-      </c>
-      <c r="F9">
-        <v>15326</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D15">
+        <v>15326</v>
+      </c>
+      <c r="E15">
+        <v>15326</v>
+      </c>
+      <c r="F15" t="s">
         <v>49</v>
       </c>
-      <c r="I9" t="s">
+      <c r="H15" t="s">
         <v>54</v>
       </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
-        <v>3249</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>15326</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
-        <v>3250</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11">
-        <v>15326</v>
-      </c>
-      <c r="G11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1">
-        <v>3251</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12">
-        <v>15326</v>
-      </c>
-      <c r="G12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1">
-        <v>3252</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13">
-        <v>15326</v>
-      </c>
-      <c r="G13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1">
-        <v>3253</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14">
-        <v>15326</v>
-      </c>
-      <c r="F14">
-        <v>15326</v>
-      </c>
-      <c r="G14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1">
-        <v>3254</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15">
-        <v>15326</v>
-      </c>
-      <c r="F15">
-        <v>15326</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1">
-        <v>4762</v>
-      </c>
-      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="F16">
+      <c r="E16">
         <v>23748</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F16" t="s">
         <v>50</v>
       </c>
+      <c r="H16" t="s">
+        <v>55</v>
+      </c>
       <c r="I16" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1">
-        <v>4763</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
         <v>44</v>
+      </c>
+      <c r="D17">
+        <v>23748</v>
       </c>
       <c r="E17">
         <v>23748</v>
       </c>
-      <c r="F17">
-        <v>23748</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F17" t="s">
         <v>50</v>
       </c>
+      <c r="H17" t="s">
+        <v>55</v>
+      </c>
       <c r="I17" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="1">
-        <v>7301</v>
-      </c>
-      <c r="B18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
         <v>13212</v>
       </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
       <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18">
+        <v>36381</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19">
+        <v>13212</v>
+      </c>
+      <c r="E19" t="s">
         <v>46</v>
       </c>
-      <c r="G18" t="s">
+      <c r="F19" t="s">
         <v>51</v>
       </c>
-      <c r="H18">
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21">
         <v>36381</v>
       </c>
-      <c r="I18" t="s">
+      <c r="H21" t="s">
         <v>56</v>
       </c>
-      <c r="J18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="1">
-        <v>7302</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22">
+        <v>36381</v>
+      </c>
+      <c r="H22" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23">
+        <v>36372</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24">
+        <v>36381</v>
+      </c>
+      <c r="H24" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19">
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25">
+        <v>36381</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="E26">
         <v>13212</v>
       </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="F26" t="s">
         <v>51</v>
       </c>
-      <c r="I19" t="s">
+      <c r="H26" t="s">
         <v>56</v>
       </c>
-      <c r="J19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="1">
-        <v>7303</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1">
-        <v>7304</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21">
-        <v>36381</v>
-      </c>
-      <c r="I21" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="1">
-        <v>7305</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22">
-        <v>36381</v>
-      </c>
-      <c r="I22" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1">
-        <v>7306</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23">
-        <v>36372</v>
-      </c>
-      <c r="I23" t="s">
-        <v>56</v>
-      </c>
-      <c r="J23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="1">
-        <v>7307</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24">
-        <v>36381</v>
-      </c>
-      <c r="I24" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="1">
-        <v>7308</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H25">
-        <v>36381</v>
-      </c>
-      <c r="I25" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="1">
-        <v>7888</v>
-      </c>
-      <c r="F26">
-        <v>13212</v>
-      </c>
-      <c r="G26" t="s">
-        <v>51</v>
-      </c>
       <c r="I26" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
